--- a/examples/financials_clean.xlsx
+++ b/examples/financials_clean.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>18900000</v>
+        <v>15800000</v>
       </c>
     </row>
     <row r="18">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>8400000</v>
+        <v>7200000</v>
       </c>
     </row>
     <row r="19">
